--- a/Result/profitability/2228.xlsx
+++ b/Result/profitability/2228.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM66"/>
+  <dimension ref="A1:AM67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.53</v>
       </c>
       <c r="M2" t="n">
-        <v>1.535</v>
+        <v>1.42125</v>
       </c>
       <c r="N2" t="n">
-        <v>24.495</v>
+        <v>23.8125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.58</v>
       </c>
       <c r="M3" t="n">
-        <v>1.50875</v>
+        <v>1.26375</v>
       </c>
       <c r="N3" t="n">
-        <v>24.6025</v>
+        <v>24.42375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.53</v>
       </c>
       <c r="M4" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>24.97125</v>
+        <v>24.48375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.59</v>
       </c>
       <c r="M5" t="n">
-        <v>1.18875</v>
+        <v>1.1625</v>
       </c>
       <c r="N5" t="n">
-        <v>25.59625</v>
+        <v>25.29125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>2.13</v>
       </c>
       <c r="M6" t="n">
-        <v>1.31875</v>
+        <v>1.28875</v>
       </c>
       <c r="N6" t="n">
-        <v>26.46125</v>
+        <v>26.0825</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>2.07</v>
       </c>
       <c r="M7" t="n">
-        <v>1.4375</v>
+        <v>1.3975</v>
       </c>
       <c r="N7" t="n">
-        <v>27.6625</v>
+        <v>27.5975</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -8810,6 +8810,133 @@
       </c>
       <c r="AM66" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2228</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1214</v>
+      </c>
+      <c r="D67" t="n">
+        <v>958</v>
+      </c>
+      <c r="E67" t="n">
+        <v>256</v>
+      </c>
+      <c r="F67" t="n">
+        <v>21.09</v>
+      </c>
+      <c r="G67" t="n">
+        <v>86</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>7.11%</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>7</v>
+      </c>
+      <c r="J67" t="n">
+        <v>93</v>
+      </c>
+      <c r="K67" t="n">
+        <v>70</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1.45375</v>
+      </c>
+      <c r="N67" t="n">
+        <v>23.35</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
+      </c>
+      <c r="V67" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="X67" t="n">
+        <v>0.01149425287356332</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>-1.300000000000001</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>-0.0580616346583297</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>-0.2100000000000001</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>-0.1926605504587157</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>-2.440000000000001</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>-0.1036974075648109</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK67" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
